--- a/engine/phdc_study/PHDC_Valuation_Model_30082026.xlsx
+++ b/engine/phdc_study/PHDC_Valuation_Model_30082026.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,6 +128,7 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -741,7 +742,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cash Flow — forecast</t>
+          <t>Cash flow — forecast</t>
         </is>
       </c>
     </row>
@@ -1189,24 +1190,24 @@
           <t>Cash conversion</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B4" s="26" t="n">
         <v>0.2225000851091698</v>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="26" t="n">
         <v>0.2425000851091698</v>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.2625000851091698</v>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.2825000851091698</v>
       </c>
-      <c r="F4" s="25" t="n">
+      <c r="F4" s="26" t="n">
         <v>0.3025000851091698</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="n">
+      <c r="A5" s="27" t="n">
         <v>0.03937593483976742</v>
       </c>
       <c r="B5" s="7" t="n">
@@ -1226,7 +1227,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="n">
+      <c r="A6" s="27" t="n">
         <v>0.06</v>
       </c>
       <c r="B6" s="7" t="n">
@@ -1246,7 +1247,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="n">
+      <c r="A7" s="27" t="n">
         <v>0.08713663734609707</v>
       </c>
       <c r="B7" s="7" t="n">
@@ -1266,7 +1267,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="n">
+      <c r="A8" s="27" t="n">
         <v>0.12</v>
       </c>
       <c r="B8" s="7" t="n">
@@ -1286,7 +1287,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="27" t="n">
         <v>0.1787001284632628</v>
       </c>
       <c r="B9" s="7" t="n">
@@ -1458,7 +1459,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1505,19 +1506,19 @@
           <t>Talaat Moustafa Group Holding</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="29" t="n">
         <v>1.4718</v>
       </c>
-      <c r="D5" s="24" t="n">
+      <c r="D5" s="25" t="n">
         <v>0.3261</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="30" t="n">
         <v>0.1848</v>
       </c>
-      <c r="F5" s="24" t="n">
+      <c r="F5" s="25" t="n">
         <v>0.4394</v>
       </c>
-      <c r="G5" s="24" t="n">
+      <c r="G5" s="25" t="n">
         <v>-0.4419</v>
       </c>
     </row>
@@ -1532,19 +1533,19 @@
           <t>Palm Hills Developments</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="29" t="n">
         <v>1.0493</v>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="25" t="n">
         <v>0.2988</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="30" t="n">
         <v>0.1823</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="25" t="n">
         <v>0.4391</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="25" t="n">
         <v>-0.4866</v>
       </c>
     </row>
@@ -1559,19 +1560,19 @@
           <t>Orascom Development Egypt</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="29" t="n">
         <v>0.8837</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="25" t="n">
         <v>0.321</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="30" t="n">
         <v>0.173</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="25" t="n">
         <v>0.4636</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="25" t="n">
         <v>-0.4293</v>
       </c>
     </row>
@@ -1586,19 +1587,19 @@
           <t>Heliopolis Housing and Development</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="29" t="n">
         <v>0.7653</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="25" t="n">
         <v>0.2884</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="30" t="n">
         <v>0.1815</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="25" t="n">
         <v>0.444</v>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="25" t="n">
         <v>-0.3958</v>
       </c>
     </row>
@@ -1613,19 +1614,19 @@
           <t>Emaar Misr for Development</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="29" t="n">
         <v>0.7388</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="25" t="n">
         <v>0.2441</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="30" t="n">
         <v>0.1692</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="25" t="n">
         <v>0.4106</v>
       </c>
-      <c r="G9" s="24" t="n">
+      <c r="G9" s="25" t="n">
         <v>-0.4712</v>
       </c>
     </row>
@@ -1640,19 +1641,19 @@
           <t>Pioneers Properties for Urban Development</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="29" t="n">
         <v>0.7067</v>
       </c>
-      <c r="D10" s="24" t="n">
+      <c r="D10" s="25" t="n">
         <v>0.2576</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="30" t="n">
         <v>0.1864</v>
       </c>
-      <c r="F10" s="24" t="n">
+      <c r="F10" s="25" t="n">
         <v>0.4217</v>
       </c>
-      <c r="G10" s="24" t="n">
+      <c r="G10" s="25" t="n">
         <v>-0.5199</v>
       </c>
     </row>
@@ -1667,24 +1668,24 @@
           <t>Sixth of October Development &amp; Investment (SODIC)</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="29" t="n">
         <v>0.4938</v>
       </c>
-      <c r="D11" s="24" t="n">
+      <c r="D11" s="25" t="n">
         <v>0.1033</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="30" t="n">
         <v>0.2237</v>
       </c>
-      <c r="F11" s="24" t="n">
+      <c r="F11" s="25" t="n">
         <v>0.4713</v>
       </c>
-      <c r="G11" s="24" t="n">
+      <c r="G11" s="25" t="n">
         <v>-0.4658</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>Earnings and book multiples are not published for the peer group: no peer discloses statements this study can obtain on a consistent basis, and an inconsistent multiple would mislead.</t>
         </is>
@@ -1701,7 +1702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1728,153 +1729,275 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Valuation</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Per share (EGP)</t>
+          <t>Bear</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Equity (EGP mn)</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Enterprise value</t>
+          <t>Full value</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Weight</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Weak cash conversion (3.9%)</t>
+          <t>Discounted cash flow</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>9.17</v>
+        <v>2.85</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>26215</v>
+        <v>14.86</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>45704</v>
+        <v>38.75</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Average cash conversion (8.7%)</t>
+          <t>Book value of equity</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>19.3</v>
+        <v>5.91</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>55208</v>
+        <v>6.56</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>74697</v>
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Strong cash conversion (17.9%)</t>
+          <t>Earnings multiple on own history</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>38.74</v>
+        <v>7.45</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>110792</v>
+        <v>11.17</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>130281</v>
+        <v>17.37</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Average, alternative country-risk basis</t>
+          <t>Normalised earnings power</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>21.44</v>
+        <v>4.72</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>61314</v>
+        <v>5.17</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>80803</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Market price, 23 Aug 2026</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>15.2</v>
+        <v>5.72</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Weighted central</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Book value of equity per share</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>6.56</v>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Valuation</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Per share (EGP)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Equity (EGP mn)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Cash conversion implied by the market price</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="n">
-        <v>0.0678</v>
+          <t>Weak cash conversion (3.9%)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>26215</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>45704</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Average cash conversion (8.7%)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>55208</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>74697</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Cost of capital</t>
-        </is>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Strong cash conversion (17.9%)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>38.74</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>110792</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>130281</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Weighted average, rating basis</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>0.2625000851091698</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Weighted average, swap basis</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>0.2523786184712106</v>
+          <t>Average, alternative country-risk basis</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>61314</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>80803</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
+          <t>Market price, 23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Book value of equity per share</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Cash conversion implied by the market price</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>0.0678</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Cost of capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Weighted average, rating basis</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>0.2625000851091698</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Weighted average, swap basis</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>0.2523786184712106</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
           <t>Previous edition used</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B24" s="9" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -2475,169 +2598,485 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Segments and operating drivers</t>
+          <t>Units and prices by region — the forecast's drivers</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>What the company discloses, and at what level the forecast is built.</t>
+          <t>New sales value and unit counts are both disclosed per region; the price per unit is one divided by the other.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>Disclosed driver</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Note</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>North Coast &amp; Alexandria</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>New sales, 1Q2026 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="n">
-        <v>52000</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>includes EGP 24,000mn from one land-plot launch</t>
-        </is>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2024</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>New sales, FY2024 (EGP mn)</t>
+          <t>New sales (EGP mn)</t>
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>151016</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>chart series</t>
-        </is>
+        <v>4205</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>7139</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>5627</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>13900</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>95082</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Order book, 31 Mar 2026 (EGP mn)</t>
+          <t>Units sold</t>
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>263000</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>units sold and not yet delivered</t>
-        </is>
+        <v>726</v>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>1552</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>800</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>1231</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>4192</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Order book, FY2024 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="n">
-        <v>147000</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
+          <t>Price per unit (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>5.792011019283747</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>4.599871134020619</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>7.03375</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>11.29163281884647</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>22.68177480916031</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Units sold, FY2023</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>5300</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>the last year the company disclosed a unit count</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Units delivered, FY2023</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>carried forward at 2074 units, price 22.68, escalated</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Construction spend, FY2024 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>8500</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>West Cairo &amp; Badya</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Cash collections, FY2024 (EGP mn)</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n">
-        <v>25400</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2024</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>New sales (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>6627</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>7258</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>13118</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>32332</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>44570</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Units sold</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>858</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>1416</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>2950</v>
+      </c>
+      <c r="F14" s="15" t="n">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Price per unit (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>7.723776223776224</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>5.125706214689266</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>6.433545855811673</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>10.96</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>15.69918985558295</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>carried forward at 2609 units, price 15.70, escalated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>East Cairo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>New sales (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>1947</v>
+      </c>
+      <c r="C20" s="15" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>7265</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>13270</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>11364</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Units sold</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>256</v>
+      </c>
+      <c r="C21" s="15" t="n">
+        <v>382</v>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>1194</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Price per unit (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>7.60546875</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>7.570680628272251</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>6.084589614740368</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>11.05833333333333</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>25.08609271523179</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>carried forward at 949 units, price 25.09, escalated</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Disclosed group drivers</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Disclosed driver</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>New sales, 1Q2026 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>52000</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>includes EGP 24,000mn from one land-plot launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>New sales, FY2024 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="n">
+        <v>151016</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>chart series</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Order book, 31 Mar 2026 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="n">
+        <v>263000</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>units sold and not yet delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Order book, FY2024 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>147000</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Units sold, FY2023</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="n">
+        <v>5300</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>the last year the company disclosed a unit count</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Units delivered, FY2023</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Construction spend, FY2024 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Cash collections, FY2024 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>25400</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
           <t>Land bank (mn sqm)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B35" s="13" t="n">
         <v>33</v>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Build level: SEGMENT, not unit.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>The company discloses no per-project unit mix, unit area, price per square metre or construction cost per square metre. The forecast is built at the finest level the disclosure supports and the limit is stated rather than filled.</t>
         </is>
@@ -3258,303 +3697,403 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Income Statement — forecast</t>
+          <t>Income statement — built from units and prices</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Central case. EGP million.</t>
+          <t>Gross margin is an OUTPUT of price per unit against cost per unit.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>EGP million</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="n">
+          <t>EGP mn unless stated</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>2026</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="5" t="n">
         <v>2027</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="5" t="n">
         <v>2028</v>
       </c>
-      <c r="E4" s="20" t="n">
+      <c r="E4" s="5" t="n">
         <v>2029</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" s="5" t="n">
         <v>2030</v>
-      </c>
-      <c r="G4" s="20" t="n">
-        <v>2031</v>
-      </c>
-      <c r="H4" s="20" t="n">
-        <v>2032</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>2033</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>2034</v>
-      </c>
-      <c r="K4" s="20" t="n">
-        <v>2035</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Units sold</t>
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>45284</v>
+        <v>5632.6667</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>56695.5</v>
+        <v>5632.6667</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>70982.8</v>
+        <v>5632.6667</v>
       </c>
       <c r="E5" s="23" t="n">
-        <v>88870.5</v>
+        <v>5632.6667</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>111265.8</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>139304.8</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <v>174409.6</v>
-      </c>
-      <c r="I5" s="23" t="n">
-        <v>218360.8</v>
-      </c>
-      <c r="J5" s="23" t="n">
-        <v>273387.8</v>
-      </c>
-      <c r="K5" s="23" t="n">
-        <v>342281.5</v>
+        <v>5632.6667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>New sales</t>
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>17353.9</v>
+        <v>139999.495</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>21727.1</v>
+        <v>175279.3678</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>27202.3</v>
+        <v>219449.7685</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>34057.3</v>
+        <v>274751.1101</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>42639.7</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>53384.9</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <v>66837.89999999999</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <v>83681.10000000001</v>
-      </c>
-      <c r="J6" s="23" t="n">
-        <v>104768.7</v>
-      </c>
-      <c r="K6" s="23" t="n">
-        <v>131170.4</v>
+        <v>343988.3898</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
+          <t>Units delivered</t>
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>0</v>
+        <v>1885.5495</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>0</v>
+        <v>2168.3819</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>0</v>
+        <v>2493.6392</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>0</v>
+        <v>2867.6851</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="23" t="n">
-        <v>0</v>
+        <v>3297.8379</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Pre-tax profit</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="n">
-        <v>828.2</v>
-      </c>
-      <c r="C8" s="23" t="n">
-        <v>3193</v>
-      </c>
-      <c r="D8" s="23" t="n">
-        <v>6153.8</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>9860.6</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>14501.6</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>20312.1</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <v>27586.8</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <v>36694.8</v>
-      </c>
-      <c r="J8" s="23" t="n">
-        <v>48098</v>
-      </c>
-      <c r="K8" s="23" t="n">
-        <v>62374.8</v>
+          <t>Revenue per delivered unit</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>21.2924</v>
+      </c>
+      <c r="C8" s="24" t="n">
+        <v>26.6581</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>33.376</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>41.7867</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>52.317</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Tax</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>186.3</v>
+        <v>40147.923</v>
       </c>
       <c r="C9" s="23" t="n">
-        <v>718.4</v>
+        <v>57804.9795</v>
       </c>
       <c r="D9" s="23" t="n">
-        <v>1384.6</v>
+        <v>83227.60950000001</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>2218.6</v>
+        <v>119831.1122</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>3262.9</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>4570.2</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>6207</v>
-      </c>
-      <c r="I9" s="23" t="n">
-        <v>8256.299999999999</v>
-      </c>
-      <c r="J9" s="23" t="n">
-        <v>10822</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>14034.3</v>
+        <v>172532.8354</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>Cost per delivered unit</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>13.1327</v>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>16.4421</v>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>20.5855</v>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>25.773</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>32.2679</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Cost of revenue</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>24762.2864</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>35652.74</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>51332.815</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>73908.98699999999</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>106414.1595</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>15385.6366</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>22152.2396</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <v>31894.7945</v>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>45922.1252</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>66118.6758</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B10" s="24">
-        <f>B6/B5</f>
-        <v/>
-      </c>
-      <c r="C10" s="24">
-        <f>C6/C5</f>
-        <v/>
-      </c>
-      <c r="D10" s="24">
-        <f>D6/D5</f>
-        <v/>
-      </c>
-      <c r="E10" s="24">
-        <f>E6/E5</f>
-        <v/>
-      </c>
-      <c r="F10" s="24">
-        <f>F6/F5</f>
-        <v/>
-      </c>
-      <c r="G10" s="24">
-        <f>G6/G5</f>
-        <v/>
-      </c>
-      <c r="H10" s="24">
-        <f>H6/H5</f>
-        <v/>
-      </c>
-      <c r="I10" s="24">
-        <f>I6/I5</f>
-        <v/>
-      </c>
-      <c r="J10" s="24">
-        <f>J6/J5</f>
-        <v/>
-      </c>
-      <c r="K10" s="24">
-        <f>K6/K5</f>
-        <v/>
+      <c r="B13" s="25" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>0.3832</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Overheads</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>7065.816</v>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>10173.3619</v>
+      </c>
+      <c r="D14" s="23" t="n">
+        <v>14647.6064</v>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>21089.6237</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>30364.8403</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Operating profit</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>7927.2136</v>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>11413.6021</v>
+      </c>
+      <c r="D15" s="23" t="n">
+        <v>16433.3044</v>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>23660.6716</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>34066.635</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Finance cost</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="D16" s="23" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>3347.5</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>3347.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>4579.7136</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>8066.1021</v>
+      </c>
+      <c r="D17" s="23" t="n">
+        <v>13085.8044</v>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>20313.1716</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>30719.135</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Net profit</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>3549.278</v>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>6251.2292</v>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>10141.4984</v>
+      </c>
+      <c r="E18" s="23" t="n">
+        <v>15742.708</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>23807.3296</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Earnings per share (EGP)</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>1.241</v>
+      </c>
+      <c r="C19" s="24" t="n">
+        <v>2.1858</v>
+      </c>
+      <c r="D19" s="24" t="n">
+        <v>3.5461</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>5.5046</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>8.3245</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Order book, closing</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>362851.572</v>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>480325.9603</v>
+      </c>
+      <c r="D20" s="23" t="n">
+        <v>616548.1192</v>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>771468.1171</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>942923.6716</v>
       </c>
     </row>
   </sheetData>

--- a/engine/phdc_study/PHDC_Valuation_Model_30082026.xlsx
+++ b/engine/phdc_study/PHDC_Valuation_Model_30082026.xlsx
@@ -31,11 +31,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="#,##0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -97,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,7 +115,6 @@
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -126,14 +126,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -571,36 +574,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Balance sheet — as reported</t>
+          <t>Balance sheet — as reported, then forecast both ways</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EGP million.</t>
+          <t>EGP million. Assets equal liabilities plus shareholders' funds in every reported and every forecast year.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>AS REPORTED</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
@@ -710,6 +720,1218 @@
       <c r="C12" s="7">
         <f>C7-C10-C11</f>
         <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>FORECAST — IF CASH CONVERSION HOLDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn unless stated</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>2029</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Trade and notes receivable</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="n">
+        <v>104247.5434</v>
+      </c>
+      <c r="C16" s="20" t="n">
+        <v>107203.1736</v>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>113353.7011</v>
+      </c>
+      <c r="E16" s="20" t="n">
+        <v>124104.2418</v>
+      </c>
+      <c r="F16" s="20" t="n">
+        <v>141477.8814</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Work in progress</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n">
+        <v>17695.9447</v>
+      </c>
+      <c r="C17" s="20" t="n">
+        <v>18197.6608</v>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>19241.7083</v>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>21066.6048</v>
+      </c>
+      <c r="F17" s="20" t="n">
+        <v>24015.7675</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Other receivables and prepayments</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="n">
+        <v>13013.9604</v>
+      </c>
+      <c r="C18" s="20" t="n">
+        <v>13382.9327</v>
+      </c>
+      <c r="D18" s="20" t="n">
+        <v>14150.7467</v>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>15492.813</v>
+      </c>
+      <c r="F18" s="20" t="n">
+        <v>17661.6876</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Advances to suppliers</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>9120.6492</v>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>9379.2381</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>9917.349700000001</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>10857.9177</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v>12377.9427</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Cash and equivalents</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>12516.3758</v>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>16975.2575</v>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>23395.1555</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>32638.5245</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>45947.1273</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Property and equipment</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>4530.8722</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>4543.6465</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>4562.0388</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>4588.5201</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <v>4626.6479</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Other assets, held at the 2025 level</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="C22" s="20" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="D22" s="20" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="E22" s="20" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="F22" s="20" t="n">
+        <v>15128.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="n">
+        <v>176253.6456</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>184810.2092</v>
+      </c>
+      <c r="D23" s="21" t="n">
+        <v>199749.0001</v>
+      </c>
+      <c r="E23" s="21" t="n">
+        <v>223876.9219</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>261235.3543</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Customer advances</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n">
+        <v>69847.66379999999</v>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>71827.9874</v>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>75948.9476</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>83151.99649999999</v>
+      </c>
+      <c r="F24" s="20" t="n">
+        <v>94792.6367</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Suppliers</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>3834.0928</v>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>3942.7972</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>4169.0058</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>4564.3971</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>5203.3776</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Other creditors</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>5158.149</v>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>5304.393</v>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>5608.72</v>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>6140.6547</v>
+      </c>
+      <c r="F26" s="20" t="n">
+        <v>7000.2991</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Cheques under collection</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>2471.1619</v>
+      </c>
+      <c r="C27" s="20" t="n">
+        <v>2541.2244</v>
+      </c>
+      <c r="D27" s="20" t="n">
+        <v>2687.0211</v>
+      </c>
+      <c r="E27" s="20" t="n">
+        <v>2941.86</v>
+      </c>
+      <c r="F27" s="20" t="n">
+        <v>3353.6978</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Borrowings</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="C28" s="20" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>33552.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities, held at the 2025 level</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="C29" s="20" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>39074.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="n">
+        <v>153938.5676</v>
+      </c>
+      <c r="C30" s="21" t="n">
+        <v>156243.902</v>
+      </c>
+      <c r="D30" s="21" t="n">
+        <v>161041.1945</v>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>169426.4083</v>
+      </c>
+      <c r="F30" s="21" t="n">
+        <v>182977.5112</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Shareholders' funds</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n">
+        <v>22315.078</v>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>28566.3072</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>38707.8056</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>54450.5136</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>78257.8432</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL LIABILITIES AND EQUITY</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="n">
+        <v>176253.6456</v>
+      </c>
+      <c r="C32" s="21" t="n">
+        <v>184810.2092</v>
+      </c>
+      <c r="D32" s="21" t="n">
+        <v>199749.0001</v>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>223876.9219</v>
+      </c>
+      <c r="F32" s="21" t="n">
+        <v>261235.3543</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Check: assets less liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D33" s="26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E33" s="26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F33" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Collection period, days</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="n">
+        <v>947.754</v>
+      </c>
+      <c r="C34" s="20" t="n">
+        <v>676.9167</v>
+      </c>
+      <c r="D34" s="20" t="n">
+        <v>497.1199</v>
+      </c>
+      <c r="E34" s="20" t="n">
+        <v>378.0158</v>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>299.302</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Work in progress, days of cost</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="n">
+        <v>260.841</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>186.3011</v>
+      </c>
+      <c r="D35" s="20" t="n">
+        <v>136.8174</v>
+      </c>
+      <c r="E35" s="20" t="n">
+        <v>104.0376</v>
+      </c>
+      <c r="F35" s="20" t="n">
+        <v>82.374</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Suppliers, days of cost</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="n">
+        <v>56.5151</v>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>40.3649</v>
+      </c>
+      <c r="D36" s="20" t="n">
+        <v>29.6436</v>
+      </c>
+      <c r="E36" s="20" t="n">
+        <v>22.5413</v>
+      </c>
+      <c r="F36" s="20" t="n">
+        <v>17.8476</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Customer advances, share of the order book</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>0.1925</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>0.1232</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>0.1005</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Net working capital</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="n">
+        <v>62767.03</v>
+      </c>
+      <c r="C38" s="20" t="n">
+        <v>64546.6032</v>
+      </c>
+      <c r="D38" s="20" t="n">
+        <v>68249.8113</v>
+      </c>
+      <c r="E38" s="20" t="n">
+        <v>74722.66899999999</v>
+      </c>
+      <c r="F38" s="20" t="n">
+        <v>85183.268</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  as a multiple of revenue</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>1.5634</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>1.1166</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>0.6236</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>0.4937</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>FORECAST — IF THE COLLECTION CYCLE HOLDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn unless stated</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C42" s="19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D42" s="19" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E42" s="19" t="n">
+        <v>2029</v>
+      </c>
+      <c r="F42" s="19" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Trade and notes receivable</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n">
+        <v>114897.099</v>
+      </c>
+      <c r="C43" s="20" t="n">
+        <v>165428.8431</v>
+      </c>
+      <c r="D43" s="20" t="n">
+        <v>238184.4484</v>
+      </c>
+      <c r="E43" s="20" t="n">
+        <v>342937.9687</v>
+      </c>
+      <c r="F43" s="20" t="n">
+        <v>493762.0874</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Work in progress</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n">
+        <v>19503.699</v>
+      </c>
+      <c r="C44" s="20" t="n">
+        <v>28081.4258</v>
+      </c>
+      <c r="D44" s="20" t="n">
+        <v>40431.6369</v>
+      </c>
+      <c r="E44" s="20" t="n">
+        <v>58213.4708</v>
+      </c>
+      <c r="F44" s="20" t="n">
+        <v>83815.7553</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Other receivables and prepayments</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>14343.42</v>
+      </c>
+      <c r="C45" s="20" t="n">
+        <v>20651.6561</v>
+      </c>
+      <c r="D45" s="20" t="n">
+        <v>29734.2545</v>
+      </c>
+      <c r="E45" s="20" t="n">
+        <v>42811.3796</v>
+      </c>
+      <c r="F45" s="20" t="n">
+        <v>61639.8243</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Advances to suppliers</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="n">
+        <v>10052.382</v>
+      </c>
+      <c r="C46" s="20" t="n">
+        <v>14473.4196</v>
+      </c>
+      <c r="D46" s="20" t="n">
+        <v>20838.8295</v>
+      </c>
+      <c r="E46" s="20" t="n">
+        <v>30003.7468</v>
+      </c>
+      <c r="F46" s="20" t="n">
+        <v>43199.3946</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Cash and equivalents</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n">
+        <v>6104.3208</v>
+      </c>
+      <c r="C47" s="20" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="D47" s="20" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="E47" s="20" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="F47" s="20" t="n">
+        <v>2354.875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Property and equipment</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="n">
+        <v>4530.8722</v>
+      </c>
+      <c r="C48" s="20" t="n">
+        <v>4543.6465</v>
+      </c>
+      <c r="D48" s="20" t="n">
+        <v>4562.0388</v>
+      </c>
+      <c r="E48" s="20" t="n">
+        <v>4588.5201</v>
+      </c>
+      <c r="F48" s="20" t="n">
+        <v>4626.6479</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Other assets, held at the 2025 level</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="C49" s="20" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="D49" s="20" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="E49" s="20" t="n">
+        <v>15128.3</v>
+      </c>
+      <c r="F49" s="20" t="n">
+        <v>15128.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL ASSETS</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="n">
+        <v>184560.093</v>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>250662.1661</v>
+      </c>
+      <c r="D50" s="21" t="n">
+        <v>351234.3831</v>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>496038.261</v>
+      </c>
+      <c r="F50" s="21" t="n">
+        <v>704526.8845</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Customer advances</t>
+        </is>
+      </c>
+      <c r="B51" s="20" t="n">
+        <v>76983.05100000001</v>
+      </c>
+      <c r="C51" s="20" t="n">
+        <v>110840.1968</v>
+      </c>
+      <c r="D51" s="20" t="n">
+        <v>159587.7154</v>
+      </c>
+      <c r="E51" s="20" t="n">
+        <v>229774.3926</v>
+      </c>
+      <c r="F51" s="20" t="n">
+        <v>330829.1705</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Suppliers</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="n">
+        <v>4225.77</v>
+      </c>
+      <c r="C52" s="20" t="n">
+        <v>6084.2636</v>
+      </c>
+      <c r="D52" s="20" t="n">
+        <v>8760.122799999999</v>
+      </c>
+      <c r="E52" s="20" t="n">
+        <v>12612.8248</v>
+      </c>
+      <c r="F52" s="20" t="n">
+        <v>18159.9452</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Other creditors</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="n">
+        <v>5685.087</v>
+      </c>
+      <c r="C53" s="20" t="n">
+        <v>8185.3883</v>
+      </c>
+      <c r="D53" s="20" t="n">
+        <v>11785.322</v>
+      </c>
+      <c r="E53" s="20" t="n">
+        <v>16968.5066</v>
+      </c>
+      <c r="F53" s="20" t="n">
+        <v>24431.2559</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Cheques under collection</t>
+        </is>
+      </c>
+      <c r="B54" s="20" t="n">
+        <v>2723.607</v>
+      </c>
+      <c r="C54" s="20" t="n">
+        <v>3921.4494</v>
+      </c>
+      <c r="D54" s="20" t="n">
+        <v>5646.1028</v>
+      </c>
+      <c r="E54" s="20" t="n">
+        <v>8129.2588</v>
+      </c>
+      <c r="F54" s="20" t="n">
+        <v>11704.5068</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Borrowings</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n">
+        <v>33552.7</v>
+      </c>
+      <c r="C55" s="20" t="n">
+        <v>53989.7609</v>
+      </c>
+      <c r="D55" s="20" t="n">
+        <v>87672.5145</v>
+      </c>
+      <c r="E55" s="20" t="n">
+        <v>135027.9646</v>
+      </c>
+      <c r="F55" s="20" t="n">
+        <v>202069.363</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities, held at the 2025 level</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="C56" s="20" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="D56" s="20" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="E56" s="20" t="n">
+        <v>39074.8</v>
+      </c>
+      <c r="F56" s="20" t="n">
+        <v>39074.8</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL LIABILITIES</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="n">
+        <v>162245.015</v>
+      </c>
+      <c r="C57" s="21" t="n">
+        <v>222095.859</v>
+      </c>
+      <c r="D57" s="21" t="n">
+        <v>312526.5775</v>
+      </c>
+      <c r="E57" s="21" t="n">
+        <v>441587.7475</v>
+      </c>
+      <c r="F57" s="21" t="n">
+        <v>626269.0413</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Shareholders' funds</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="n">
+        <v>22315.078</v>
+      </c>
+      <c r="C58" s="20" t="n">
+        <v>28566.3072</v>
+      </c>
+      <c r="D58" s="20" t="n">
+        <v>38707.8056</v>
+      </c>
+      <c r="E58" s="20" t="n">
+        <v>54450.5136</v>
+      </c>
+      <c r="F58" s="20" t="n">
+        <v>78257.8432</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL LIABILITIES AND EQUITY</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="n">
+        <v>184560.093</v>
+      </c>
+      <c r="C59" s="21" t="n">
+        <v>250662.1661</v>
+      </c>
+      <c r="D59" s="21" t="n">
+        <v>351234.3831</v>
+      </c>
+      <c r="E59" s="21" t="n">
+        <v>496038.261</v>
+      </c>
+      <c r="F59" s="21" t="n">
+        <v>704526.8845</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Check: assets less liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="26" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Collection period, days</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="C61" s="20" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="D61" s="20" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="E61" s="20" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="F61" s="20" t="n">
+        <v>1044.5731</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Work in progress, days of cost</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="C62" s="20" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="D62" s="20" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="E62" s="20" t="n">
+        <v>287.4876</v>
+      </c>
+      <c r="F62" s="20" t="n">
+        <v>287.4876</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Suppliers, days of cost</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="C63" s="20" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="D63" s="20" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="E63" s="20" t="n">
+        <v>62.2885</v>
+      </c>
+      <c r="F63" s="20" t="n">
+        <v>62.2885</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Customer advances, share of the order book</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="n">
+        <v>0.2122</v>
+      </c>
+      <c r="C64" s="17" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="D64" s="17" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="F64" s="17" t="n">
+        <v>0.3509</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Net working capital</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="n">
+        <v>69179.08500000001</v>
+      </c>
+      <c r="C65" s="20" t="n">
+        <v>99604.0466</v>
+      </c>
+      <c r="D65" s="20" t="n">
+        <v>143409.9063</v>
+      </c>
+      <c r="E65" s="20" t="n">
+        <v>206481.583</v>
+      </c>
+      <c r="F65" s="20" t="n">
+        <v>297292.1833</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  as a multiple of revenue</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>The cycle as reported, both audited years</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr"/>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Collection period, days</t>
+        </is>
+      </c>
+      <c r="B70" s="20" t="n">
+        <v>1044.5731</v>
+      </c>
+      <c r="C70" s="20" t="n">
+        <v>1034.7657</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Work in progress, days of cost</t>
+        </is>
+      </c>
+      <c r="B71" s="20" t="n">
+        <v>303.6796</v>
+      </c>
+      <c r="C71" s="20" t="n">
+        <v>270.3102</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Suppliers, days of cost</t>
+        </is>
+      </c>
+      <c r="B72" s="20" t="n">
+        <v>65.7968</v>
+      </c>
+      <c r="C72" s="20" t="n">
+        <v>70.12009999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Customer advances, share of the order book</t>
+        </is>
+      </c>
+      <c r="B73" s="17" t="n">
+        <v>0.2637</v>
+      </c>
+      <c r="C73" s="17" t="n">
+        <v>0.3225</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Net working capital</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="n">
+        <v>62323.5</v>
+      </c>
+      <c r="C74" s="20" t="n">
+        <v>42238.8</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  as a multiple of revenue</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>1.7231</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>1.5548</v>
       </c>
     </row>
   </sheetData>
@@ -723,145 +1945,574 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cash flow — forecast</t>
+          <t>Cash flow — forecast, both readings</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Central case. EGP million.</t>
+          <t>The audited balance sheet and the audited cash-flow statement disagree about 2025 by EGP 16,938 million, and that difference cannot be split from what is disclosed. So the forecast is published two ways and neither is averaged into the other.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>EGP million</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="n">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>IF CASH CONVERSION HOLDS — the basis of the valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn unless stated</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n">
         <v>2026</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C5" s="19" t="n">
         <v>2027</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D5" s="19" t="n">
         <v>2028</v>
       </c>
-      <c r="E4" s="20" t="n">
+      <c r="E5" s="19" t="n">
         <v>2029</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F5" s="19" t="n">
         <v>2030</v>
-      </c>
-      <c r="G4" s="20" t="n">
-        <v>2031</v>
-      </c>
-      <c r="H4" s="20" t="n">
-        <v>2032</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>2033</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>2034</v>
-      </c>
-      <c r="K4" s="20" t="n">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Operating cash flow</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="n">
-        <v>3945.9</v>
-      </c>
-      <c r="C5" s="23" t="n">
-        <v>4940.3</v>
-      </c>
-      <c r="D5" s="23" t="n">
-        <v>6185.2</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <v>7743.9</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>9695.299999999999</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>12138.6</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <v>15197.5</v>
-      </c>
-      <c r="I5" s="23" t="n">
-        <v>19027.2</v>
-      </c>
-      <c r="J5" s="23" t="n">
-        <v>23822.1</v>
-      </c>
-      <c r="K5" s="23" t="n">
-        <v>29825.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Free cash flow to the firm</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="n">
-        <v>10123.9</v>
-      </c>
-      <c r="C6" s="23" t="n">
-        <v>11004.2</v>
-      </c>
-      <c r="D6" s="23" t="n">
-        <v>12106.2</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>13486</v>
-      </c>
-      <c r="F6" s="23" t="n">
-        <v>15213.5</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>17376.4</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <v>20084.2</v>
-      </c>
-      <c r="I6" s="23" t="n">
-        <v>23474.5</v>
-      </c>
-      <c r="J6" s="23" t="n">
-        <v>27719.1</v>
-      </c>
-      <c r="K6" s="23" t="n">
-        <v>33033.3</v>
+          <t>Net profit</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>3549.278</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>6251.2292</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>10141.4984</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>15742.708</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>23807.3296</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>392.607</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>565.2756000000001</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>813.8837</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>1171.8298</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>1687.2006</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Change in working capital, cash effect</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>-443.53</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>-1779.5732</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>-3703.2081</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>-6472.8577</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>-10460.5991</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Cash from operations</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="n">
+        <v>3498.355</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>5036.9315</v>
+      </c>
+      <c r="D9" s="21" t="n">
+        <v>7252.174</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>10441.6802</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>15033.9311</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  as a share of revenue</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="C10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>0.0871</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Capital expenditure</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>-401.4792</v>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>-578.0498</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>-832.2761</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>-1198.3111</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>-1725.3284</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>New borrowing drawn</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Cash from financing</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Closing cash</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="n">
+        <v>12516.3758</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>16975.2575</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>23395.1555</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>32638.5245</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>45947.1273</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Cumulative new borrowing</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>IF THE COLLECTION CYCLE HOLDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>EGP mn unless stated</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C18" s="19" t="n">
+        <v>2027</v>
+      </c>
+      <c r="D18" s="19" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>2029</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Net profit</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>3549.278</v>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>6251.2292</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>10141.4984</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>15742.708</v>
+      </c>
+      <c r="F19" s="20" t="n">
+        <v>23807.3296</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>392.607</v>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>565.2756000000001</v>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>813.8837</v>
+      </c>
+      <c r="E20" s="20" t="n">
+        <v>1171.8298</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>1687.2006</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Change in working capital, cash effect</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>-6855.585</v>
+      </c>
+      <c r="C21" s="20" t="n">
+        <v>-30424.9616</v>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>-43805.8597</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>-63071.6768</v>
+      </c>
+      <c r="F21" s="20" t="n">
+        <v>-90810.6002</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Cash from operations</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="n">
+        <v>-2913.7</v>
+      </c>
+      <c r="C22" s="21" t="n">
+        <v>-23608.4569</v>
+      </c>
+      <c r="D22" s="21" t="n">
+        <v>-32850.4776</v>
+      </c>
+      <c r="E22" s="21" t="n">
+        <v>-46157.139</v>
+      </c>
+      <c r="F22" s="21" t="n">
+        <v>-65316.07</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  as a share of revenue</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>-0.0726</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>-0.4084</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>-0.3947</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>-0.3852</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>-0.3786</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Capital expenditure</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n">
+        <v>-401.4792</v>
+      </c>
+      <c r="C24" s="20" t="n">
+        <v>-578.0498</v>
+      </c>
+      <c r="D24" s="20" t="n">
+        <v>-832.2761</v>
+      </c>
+      <c r="E24" s="20" t="n">
+        <v>-1198.3111</v>
+      </c>
+      <c r="F24" s="20" t="n">
+        <v>-1725.3284</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>New borrowing drawn</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="20" t="n">
+        <v>20437.0609</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>33682.7537</v>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>47355.4501</v>
+      </c>
+      <c r="F25" s="20" t="n">
+        <v>67041.39840000001</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Cash from financing</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="20" t="n">
+        <v>20437.0609</v>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>33682.7537</v>
+      </c>
+      <c r="E26" s="20" t="n">
+        <v>47355.4501</v>
+      </c>
+      <c r="F26" s="20" t="n">
+        <v>67041.39840000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Closing cash</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="n">
+        <v>6104.3208</v>
+      </c>
+      <c r="C27" s="21" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>2354.875</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>2354.875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cumulative new borrowing</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="20" t="n">
+        <v>20437.0609</v>
+      </c>
+      <c r="D28" s="20" t="n">
+        <v>54119.8145</v>
+      </c>
+      <c r="E28" s="20" t="n">
+        <v>101475.2646</v>
+      </c>
+      <c r="F28" s="20" t="n">
+        <v>168516.663</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Cash conversion, the three published years</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="n">
+        <v>0.043334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="n">
+        <v>0.1787</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="n">
+        <v>0.039376</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  mean, carried above</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="n">
+        <v>0.08713700000000001</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +2526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -897,17 +2548,17 @@
           <t>EGP million</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -932,65 +2583,146 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Cost of revenue</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>5507.6</v>
+        <v>-11907.2</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>9330.1</v>
+        <v>-17739.9</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>14887.6</v>
+        <v>-21118.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Pre-tax profit</t>
+          <t>Gross profit</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>2300.7</v>
+        <v>5507.6</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>4320.6</v>
+        <v>9330.1</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>6251.1</v>
+        <v>14887.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Profit after tax and minority</t>
+          <t>Overheads</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>1581.5</v>
+        <v>-2060.5</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>3254.9</v>
+        <v>-3435.8</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>4216.7</v>
+        <v>-6365.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>Finance cost</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr"/>
+      <c r="C9" s="10" t="n">
+        <v>-2311.4</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>-3347.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Pre-tax profit</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>2300.7</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>4320.6</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>6251.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>-567.3</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>-917.1</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>-1827.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax and minority</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>1581.5</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>3254.9</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>4216.7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>Cash from operations</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B13" s="10" t="n">
         <v>756.7</v>
       </c>
-      <c r="C9" s="10" t="n">
+      <c r="C13" s="10" t="n">
         <v>4854.8</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D13" s="10" t="n">
         <v>1424.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Cash from operations, share of revenue</t>
+        </is>
+      </c>
+      <c r="B14" s="17">
+        <f>B14/B5</f>
+        <v/>
+      </c>
+      <c r="C14" s="17">
+        <f>C14/C5</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>D14/D5</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1032,12 +2764,12 @@
           <t>Percentile</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>One month</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Three months</t>
         </is>
@@ -1124,7 +2856,7 @@
           <t>Inside the 90% band</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="17" t="n">
         <v>0.9123</v>
       </c>
     </row>
@@ -1134,7 +2866,7 @@
           <t>Inside the middle band</t>
         </is>
       </c>
-      <c r="B13" s="18" t="n">
+      <c r="B13" s="17" t="n">
         <v>0.5088</v>
       </c>
     </row>
@@ -1144,7 +2876,7 @@
           <t>Band width vs a random walk</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B14" s="18" t="n">
         <v>1.469</v>
       </c>
     </row>
@@ -1190,120 +2922,120 @@
           <t>Cash conversion</t>
         </is>
       </c>
-      <c r="B4" s="26" t="n">
+      <c r="B4" s="28" t="n">
         <v>0.2225000851091698</v>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="28" t="n">
         <v>0.2425000851091698</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="28" t="n">
         <v>0.2625000851091698</v>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="28" t="n">
         <v>0.2825000851091698</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="28" t="n">
         <v>0.3025000851091698</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="n">
+      <c r="A5" s="29" t="n">
         <v>0.03937593483976742</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>15</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>11.61</v>
+        <v>6.21</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>9.17</v>
+        <v>4.29</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>7.31</v>
+        <v>2.85</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>5.86</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n">
+      <c r="A6" s="29" t="n">
         <v>0.06</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>21.6</v>
+        <v>15.56</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>16.91</v>
+        <v>11.65</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>13.54</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>11.02</v>
+        <v>6.76</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>9.050000000000001</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="n">
+      <c r="A7" s="29" t="n">
         <v>0.08713663734609707</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>30.28</v>
+        <v>24.33</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>23.87</v>
+        <v>18.81</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>19.3</v>
+        <v>14.86</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>15.89</v>
+        <v>11.91</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>13.25</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n">
+      <c r="A8" s="29" t="n">
         <v>0.12</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>40.8</v>
+        <v>34.95</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>32.31</v>
+        <v>27.48</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>26.28</v>
+        <v>22.14</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>21.79</v>
+        <v>18.14</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>18.33</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n">
+      <c r="A9" s="29" t="n">
         <v>0.1787001284632628</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>59.58</v>
+        <v>53.92</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>47.38</v>
+        <v>42.96</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>38.74</v>
+        <v>35.14</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>32.33</v>
+        <v>29.28</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>27.41</v>
+        <v>24.75</v>
       </c>
     </row>
   </sheetData>
@@ -1367,7 +3099,7 @@
           <t>Price to book</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="18" t="n">
         <v>2.3165</v>
       </c>
     </row>
@@ -1407,7 +3139,7 @@
           <t>Gross margin, 2025</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="17" t="n">
         <v>0.4116</v>
       </c>
     </row>
@@ -1417,7 +3149,7 @@
           <t>Cash conversion, 2025</t>
         </is>
       </c>
-      <c r="B12" s="18" t="n">
+      <c r="B12" s="17" t="n">
         <v>0.0394</v>
       </c>
     </row>
@@ -1459,7 +3191,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
@@ -1506,13 +3238,13 @@
           <t>Talaat Moustafa Group Holding</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="31" t="n">
         <v>1.4718</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>0.3261</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="32" t="n">
         <v>0.1848</v>
       </c>
       <c r="F5" s="25" t="n">
@@ -1533,13 +3265,13 @@
           <t>Palm Hills Developments</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="31" t="n">
         <v>1.0493</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>0.2988</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="32" t="n">
         <v>0.1823</v>
       </c>
       <c r="F6" s="25" t="n">
@@ -1560,13 +3292,13 @@
           <t>Orascom Development Egypt</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="31" t="n">
         <v>0.8837</v>
       </c>
       <c r="D7" s="25" t="n">
         <v>0.321</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="32" t="n">
         <v>0.173</v>
       </c>
       <c r="F7" s="25" t="n">
@@ -1587,13 +3319,13 @@
           <t>Heliopolis Housing and Development</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="31" t="n">
         <v>0.7653</v>
       </c>
       <c r="D8" s="25" t="n">
         <v>0.2884</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="32" t="n">
         <v>0.1815</v>
       </c>
       <c r="F8" s="25" t="n">
@@ -1614,13 +3346,13 @@
           <t>Emaar Misr for Development</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="31" t="n">
         <v>0.7388</v>
       </c>
       <c r="D9" s="25" t="n">
         <v>0.2441</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="32" t="n">
         <v>0.1692</v>
       </c>
       <c r="F9" s="25" t="n">
@@ -1641,13 +3373,13 @@
           <t>Pioneers Properties for Urban Development</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="31" t="n">
         <v>0.7067</v>
       </c>
       <c r="D10" s="25" t="n">
         <v>0.2576</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="32" t="n">
         <v>0.1864</v>
       </c>
       <c r="F10" s="25" t="n">
@@ -1668,13 +3400,13 @@
           <t>Sixth of October Development &amp; Investment (SODIC)</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="31" t="n">
         <v>0.4938</v>
       </c>
       <c r="D11" s="25" t="n">
         <v>0.1033</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="32" t="n">
         <v>0.2237</v>
       </c>
       <c r="F11" s="25" t="n">
@@ -1685,7 +3417,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>Earnings and book multiples are not published for the peer group: no peer discloses statements this study can obtain on a consistent basis, and an inconsistent multiple would mislead.</t>
         </is>
@@ -1877,13 +3609,13 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>9.17</v>
+        <v>4.29</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>26215</v>
+        <v>12270</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>45704</v>
+        <v>31759</v>
       </c>
     </row>
     <row r="13">
@@ -1893,13 +3625,13 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>19.3</v>
+        <v>14.86</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>55208</v>
+        <v>42510</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>74697</v>
+        <v>61999</v>
       </c>
     </row>
     <row r="14">
@@ -1909,13 +3641,13 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>38.74</v>
+        <v>35.14</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>110792</v>
+        <v>100485</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>130281</v>
+        <v>119975</v>
       </c>
     </row>
     <row r="15">
@@ -1925,13 +3657,13 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>21.44</v>
+        <v>16.71</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>61314</v>
+        <v>47786</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>80803</v>
+        <v>67276</v>
       </c>
     </row>
     <row r="17">
@@ -1961,7 +3693,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>0.0678</v>
+        <v>0.0887</v>
       </c>
     </row>
     <row r="21">
@@ -2040,7 +3772,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>49459.8</v>
+        <v>23030.2</v>
       </c>
     </row>
     <row r="5">
@@ -2050,7 +3782,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>25237.2</v>
+        <v>38969.3</v>
       </c>
     </row>
     <row r="6">
@@ -2152,7 +3884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2269,7 +4001,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Delivery capacity growth</t>
+          <t>Price escalation</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
@@ -2404,80 +4136,137 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Order book target multiple of revenue</t>
+          <t>Units delivered, 2026</t>
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>5.410916800712622</v>
+        <v>1885.549516413187</v>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>the 2024 level, to which the model converges</t>
+          <t>implied by the reported first quarter of 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Units delivered, annual growth</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>the disclosed run of handovers, 1,308 / 1,281 / 1,500 / 2,000</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>NOT DISCLOSED — absent by design, never estimated</t>
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Revenue per delivered unit, 2026 (EGP mn)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>21.2924257096</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>FY2024 revenue over c. 2,000 units delivered, escalated</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>fy2025 results release</t>
-        </is>
+          <t>Maintenance capital expenditure, share of revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>0.01</v>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>PHD has published FY2025 consolidated statements but NO FY2025 full-year results release. The release is where units sold, new sales, deliveries and construction spend are disclose</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>h1 2026 results</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>As at this build date (30-Aug-2026) no 2Q/H1-2026 statements or release are posted to the result centre; the newest disclosure of any kind is 1Q2026 (posted 25-Jun-2026). The study</t>
+          <t>the building itself is inventory and sits in operating cash</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>securitisation pricing</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>The EGP 2.015bn securitisation of 4-Feb-2026 discloses tranche sizes, tenors and national-scale ratings but NO coupon on any tranche, so the company's own marginal cost of debt can</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>NOT DISCLOSED — absent by design, never estimated</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>per project pricing</t>
+          <t>cash flow statement detail</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>The company does not disclose per-project unit mix, average unit area, price per square metre or construction cost per square metre. The 11-Jun-2026 edition carried a full per-proj</t>
+          <t>The FY2025 cash-flow statement is published in its three totals only (operating EGP 1,424.2mn, investing EGP -4,031.7mn, financing EGP 5,628.8mn); no line-by-line statement is post</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
+          <t>fy2025 results release</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>PHD has published FY2025 consolidated statements but NO FY2025 full-year results release. The release is where units sold, new sales, deliveries and construction spend are disclose</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>h1 2026 results</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>As at this build date (30-Aug-2026) no 2Q/H1-2026 statements or release are posted to the result centre; the newest disclosure of any kind is 1Q2026 (posted 25-Jun-2026). The study</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>securitisation pricing</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>The EGP 2.015bn securitisation of 4-Feb-2026 discloses tranche sizes, tenors and national-scale ratings but NO coupon on any tranche, so the company's own marginal cost of debt can</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>per project pricing</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>The company does not disclose per-project unit mix, average unit area, price per square metre or construction cost per square metre. The 11-Jun-2026 edition carried a full per-proj</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
           <t>backlog cost to complete</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Remaining construction cost against the EGP 263bn backlog is not disclosed as a single figure. It is inferred in the model from the realised gross margin and flagged where used.</t>
         </is>
@@ -2522,7 +4311,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>74697</v>
+        <v>61999.5</v>
       </c>
     </row>
     <row r="5">
@@ -2658,19 +4447,19 @@
           <t>New sales (EGP mn)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="14" t="n">
         <v>4205</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="14" t="n">
         <v>7139</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="14" t="n">
         <v>5627</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="14" t="n">
         <v>13900</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="14" t="n">
         <v>95082</v>
       </c>
     </row>
@@ -2680,19 +4469,19 @@
           <t>Units sold</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="14" t="n">
         <v>726</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="14" t="n">
         <v>1552</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="14" t="n">
         <v>800</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="14" t="n">
         <v>1231</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="14" t="n">
         <v>4192</v>
       </c>
     </row>
@@ -2760,19 +4549,19 @@
           <t>New sales (EGP mn)</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="14" t="n">
         <v>6627</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="14" t="n">
         <v>7258</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="14" t="n">
         <v>13118</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="14" t="n">
         <v>32332</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="14" t="n">
         <v>44570</v>
       </c>
     </row>
@@ -2782,19 +4571,19 @@
           <t>Units sold</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="14" t="n">
         <v>858</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="14" t="n">
         <v>1416</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="14" t="n">
         <v>2039</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="14" t="n">
         <v>2950</v>
       </c>
-      <c r="F14" s="15" t="n">
+      <c r="F14" s="14" t="n">
         <v>2839</v>
       </c>
     </row>
@@ -2862,19 +4651,19 @@
           <t>New sales (EGP mn)</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="14" t="n">
         <v>1947</v>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="14" t="n">
         <v>2892</v>
       </c>
-      <c r="D20" s="15" t="n">
+      <c r="D20" s="14" t="n">
         <v>7265</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="14" t="n">
         <v>13270</v>
       </c>
-      <c r="F20" s="15" t="n">
+      <c r="F20" s="14" t="n">
         <v>11364</v>
       </c>
     </row>
@@ -2884,19 +4673,19 @@
           <t>Units sold</t>
         </is>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B21" s="14" t="n">
         <v>256</v>
       </c>
-      <c r="C21" s="15" t="n">
+      <c r="C21" s="14" t="n">
         <v>382</v>
       </c>
-      <c r="D21" s="15" t="n">
+      <c r="D21" s="14" t="n">
         <v>1194</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="14" t="n">
         <v>1200</v>
       </c>
-      <c r="F21" s="15" t="n">
+      <c r="F21" s="14" t="n">
         <v>453</v>
       </c>
     </row>
@@ -2959,7 +4748,7 @@
           <t>New sales, 1Q2026 (EGP mn)</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
+      <c r="B27" s="14" t="n">
         <v>52000</v>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2974,7 +4763,7 @@
           <t>New sales, FY2024 (EGP mn)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B28" s="14" t="n">
         <v>151016</v>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2989,7 +4778,7 @@
           <t>Order book, 31 Mar 2026 (EGP mn)</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
+      <c r="B29" s="14" t="n">
         <v>263000</v>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3004,7 +4793,7 @@
           <t>Order book, FY2024 (EGP mn)</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
+      <c r="B30" s="14" t="n">
         <v>147000</v>
       </c>
       <c r="C30" s="2" t="inlineStr"/>
@@ -3015,7 +4804,7 @@
           <t>Units sold, FY2023</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n">
+      <c r="B31" s="14" t="n">
         <v>5300</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3030,7 +4819,7 @@
           <t>Units delivered, FY2023</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n">
+      <c r="B32" s="14" t="n">
         <v>1500</v>
       </c>
       <c r="C32" s="2" t="inlineStr"/>
@@ -3041,7 +4830,7 @@
           <t>Construction spend, FY2024 (EGP mn)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
+      <c r="B33" s="14" t="n">
         <v>8500</v>
       </c>
       <c r="C33" s="2" t="inlineStr"/>
@@ -3052,7 +4841,7 @@
           <t>Cash collections, FY2024 (EGP mn)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
+      <c r="B34" s="14" t="n">
         <v>25400</v>
       </c>
       <c r="C34" s="2" t="inlineStr"/>
@@ -3076,7 +4865,7 @@
       </c>
     </row>
     <row r="38" ht="44" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>The company discloses no per-project unit mix, unit area, price per square metre or construction cost per square metre. The forecast is built at the finest level the disclosure supports and the limit is stated rather than filled.</t>
         </is>
@@ -3111,17 +4900,17 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -3165,15 +4954,15 @@
           <t>Cash conversion</t>
         </is>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="17">
         <f>B6/B5</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="17">
         <f>C6/C5</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <f>D6/D5</f>
         <v/>
       </c>
@@ -3184,7 +4973,7 @@
           <t>Price to book (market)</t>
         </is>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <f>15.2000/6.5617</f>
         <v/>
       </c>
@@ -3205,7 +4994,7 @@
           <t>Return on equity, 2025</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="17">
         <f>4216.7/((18765.8+14624.7)/2)</f>
         <v/>
       </c>
@@ -3221,7 +5010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3230,11 +5019,6 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3247,7 +5031,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every row a formula off Assumptions; change a blue cell there.</t>
+          <t>Units delivered times revenue per delivered unit, then every row a formula. Change a blue cell on Assumptions and this recomputes.</t>
         </is>
       </c>
     </row>
@@ -3257,432 +5041,343 @@
           <t>EGP million</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n">
+      <c r="B4" s="19" t="n">
         <v>2026</v>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="19" t="n">
         <v>2027</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="19" t="n">
         <v>2028</v>
       </c>
-      <c r="E4" s="20" t="n">
+      <c r="E4" s="19" t="n">
         <v>2029</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" s="19" t="n">
         <v>2030</v>
-      </c>
-      <c r="G4" s="20" t="n">
-        <v>2031</v>
-      </c>
-      <c r="H4" s="20" t="n">
-        <v>2032</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>2033</v>
-      </c>
-      <c r="J4" s="20" t="n">
-        <v>2034</v>
-      </c>
-      <c r="K4" s="20" t="n">
-        <v>2035</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Delivery capacity</t>
-        </is>
-      </c>
-      <c r="B5" s="6">
-        <f>Assumptions!B17*(1+Assumptions!B10)</f>
-        <v/>
-      </c>
-      <c r="C5" s="6">
-        <f>B5*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="D5" s="6">
-        <f>C5*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="E5" s="6">
-        <f>D5*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="F5" s="6">
-        <f>E5*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="G5" s="6">
-        <f>F5*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="H5" s="6">
-        <f>G5*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="I5" s="6">
-        <f>H5*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="J5" s="6">
-        <f>I5*(1+Assumptions!$B$10)</f>
-        <v/>
-      </c>
-      <c r="K5" s="6">
-        <f>J5*(1+Assumptions!$B$10)</f>
+          <t>Units delivered</t>
+        </is>
+      </c>
+      <c r="B5" s="20">
+        <f>Assumptions!$B$19</f>
+        <v/>
+      </c>
+      <c r="C5" s="20">
+        <f>B5*(1+Assumptions!$B$20)</f>
+        <v/>
+      </c>
+      <c r="D5" s="20">
+        <f>C5*(1+Assumptions!$B$20)</f>
+        <v/>
+      </c>
+      <c r="E5" s="20">
+        <f>D5*(1+Assumptions!$B$20)</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>E5*(1+Assumptions!$B$20)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Revenue per delivered unit</t>
+        </is>
+      </c>
+      <c r="B6" s="7">
+        <f>Assumptions!$B$21</f>
+        <v/>
+      </c>
+      <c r="C6" s="7">
+        <f>B6*(1+Assumptions!$B$10)</f>
+        <v/>
+      </c>
+      <c r="D6" s="7">
+        <f>C6*(1+Assumptions!$B$10)</f>
+        <v/>
+      </c>
+      <c r="E6" s="7">
+        <f>D6*(1+Assumptions!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F6" s="7">
+        <f>E6*(1+Assumptions!$B$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B6" s="21">
-        <f>B5</f>
-        <v/>
-      </c>
-      <c r="C6" s="21">
-        <f>C5</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>D5</f>
-        <v/>
-      </c>
-      <c r="E6" s="21">
-        <f>E5</f>
-        <v/>
-      </c>
-      <c r="F6" s="21">
-        <f>F5</f>
-        <v/>
-      </c>
-      <c r="G6" s="21">
-        <f>G5</f>
-        <v/>
-      </c>
-      <c r="H6" s="21">
-        <f>H5</f>
-        <v/>
-      </c>
-      <c r="I6" s="21">
-        <f>I5</f>
-        <v/>
-      </c>
-      <c r="J6" s="21">
-        <f>J5</f>
-        <v/>
-      </c>
-      <c r="K6" s="21">
-        <f>K5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
       <c r="B7" s="21">
-        <f>B6*Assumptions!$B$8</f>
+        <f>B5*B6</f>
         <v/>
       </c>
       <c r="C7" s="21">
-        <f>C6*Assumptions!$B$8</f>
+        <f>C5*C6</f>
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>D6*Assumptions!$B$8</f>
+        <f>D5*D6</f>
         <v/>
       </c>
       <c r="E7" s="21">
-        <f>E6*Assumptions!$B$8</f>
+        <f>E5*E6</f>
         <v/>
       </c>
       <c r="F7" s="21">
-        <f>F6*Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="G7" s="21">
-        <f>G6*Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="H7" s="21">
-        <f>H6*Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="I7" s="21">
-        <f>I6*Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="J7" s="21">
-        <f>J6*Assumptions!$B$8</f>
-        <v/>
-      </c>
-      <c r="K7" s="21">
-        <f>K6*Assumptions!$B$8</f>
+        <f>F5*F6</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Overheads</t>
-        </is>
-      </c>
-      <c r="B8" s="21">
-        <f>-B6*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="C8" s="21">
-        <f>-C6*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="D8" s="21">
-        <f>-D6*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="E8" s="21">
-        <f>-E6*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="F8" s="21">
-        <f>-F6*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="G8" s="21">
-        <f>-G6*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="H8" s="21">
-        <f>-H6*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="I8" s="21">
-        <f>-I6*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="J8" s="21">
-        <f>-J6*Assumptions!$B$9</f>
-        <v/>
-      </c>
-      <c r="K8" s="21">
-        <f>-K6*Assumptions!$B$9</f>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B8" s="20">
+        <f>B7*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="C8" s="20">
+        <f>C7*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="D8" s="20">
+        <f>D7*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="E8" s="20">
+        <f>E7*Assumptions!$B$8</f>
+        <v/>
+      </c>
+      <c r="F8" s="20">
+        <f>F7*Assumptions!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>Overheads</t>
+        </is>
+      </c>
+      <c r="B9" s="20">
+        <f>-B7*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="C9" s="20">
+        <f>-C7*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="D9" s="20">
+        <f>-D7*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="E9" s="20">
+        <f>-E7*Assumptions!$B$9</f>
+        <v/>
+      </c>
+      <c r="F9" s="20">
+        <f>-F7*Assumptions!$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>Operating cash flow</t>
         </is>
       </c>
-      <c r="B9" s="21">
-        <f>B6*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="C9" s="21">
-        <f>C6*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="D9" s="21">
-        <f>D6*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="E9" s="21">
-        <f>E6*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="F9" s="21">
-        <f>F6*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="G9" s="21">
-        <f>G6*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="H9" s="21">
-        <f>H6*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="I9" s="21">
-        <f>I6*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="J9" s="21">
-        <f>J6*Assumptions!$B$5</f>
-        <v/>
-      </c>
-      <c r="K9" s="21">
-        <f>K6*Assumptions!$B$5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Free cash flow to the firm</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="n">
-        <v>10123.9</v>
-      </c>
-      <c r="C10" s="21" t="n">
-        <v>11004.2</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <v>12106.2</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>13486</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>15213.5</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>17376.4</v>
-      </c>
-      <c r="H10" s="21" t="n">
-        <v>20084.2</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>23474.5</v>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>27719.1</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>33033.3</v>
+      <c r="B10" s="20">
+        <f>B7*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="C10" s="20">
+        <f>C7*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="D10" s="20">
+        <f>D7*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="E10" s="20">
+        <f>E7*Assumptions!$B$5</f>
+        <v/>
+      </c>
+      <c r="F10" s="20">
+        <f>F7*Assumptions!$B$5</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>Maintenance capital expenditure</t>
+        </is>
+      </c>
+      <c r="B11" s="20">
+        <f>-B7*Assumptions!$B$22</f>
+        <v/>
+      </c>
+      <c r="C11" s="20">
+        <f>-C7*Assumptions!$B$22</f>
+        <v/>
+      </c>
+      <c r="D11" s="20">
+        <f>-D7*Assumptions!$B$22</f>
+        <v/>
+      </c>
+      <c r="E11" s="20">
+        <f>-E7*Assumptions!$B$22</f>
+        <v/>
+      </c>
+      <c r="F11" s="20">
+        <f>-F7*Assumptions!$B$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>plus finance cost, after tax</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>2594.3</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>2594.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Free cash flow to the firm</t>
+        </is>
+      </c>
+      <c r="B13" s="21">
+        <f>B10+B12+B11</f>
+        <v/>
+      </c>
+      <c r="C13" s="21">
+        <f>C10+C12+C11</f>
+        <v/>
+      </c>
+      <c r="D13" s="21">
+        <f>D10+D12+D11</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
+        <f>E10+E12+E11</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>F10+F12+F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B11" s="22">
+      <c r="B14" s="22">
         <f>1/(1+Assumptions!$B$12)^1</f>
         <v/>
       </c>
-      <c r="C11" s="22">
+      <c r="C14" s="22">
         <f>1/(1+Assumptions!$B$12)^2</f>
         <v/>
       </c>
-      <c r="D11" s="22">
+      <c r="D14" s="22">
         <f>1/(1+Assumptions!$B$12)^3</f>
         <v/>
       </c>
-      <c r="E11" s="22">
+      <c r="E14" s="22">
         <f>1/(1+Assumptions!$B$12)^4</f>
         <v/>
       </c>
-      <c r="F11" s="22">
+      <c r="F14" s="22">
         <f>1/(1+Assumptions!$B$12)^5</f>
-        <v/>
-      </c>
-      <c r="G11" s="22">
-        <f>1/(1+Assumptions!$B$12)^6</f>
-        <v/>
-      </c>
-      <c r="H11" s="22">
-        <f>1/(1+Assumptions!$B$12)^7</f>
-        <v/>
-      </c>
-      <c r="I11" s="22">
-        <f>1/(1+Assumptions!$B$12)^8</f>
-        <v/>
-      </c>
-      <c r="J11" s="22">
-        <f>1/(1+Assumptions!$B$12)^9</f>
-        <v/>
-      </c>
-      <c r="K11" s="22">
-        <f>1/(1+Assumptions!$B$12)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Present value</t>
-        </is>
-      </c>
-      <c r="B12" s="21">
-        <f>B10*B11</f>
-        <v/>
-      </c>
-      <c r="C12" s="21">
-        <f>C10*C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="21">
-        <f>D10*D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="21">
-        <f>E10*E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="21">
-        <f>F10*F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="21">
-        <f>G10*G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="21">
-        <f>H10*H11</f>
-        <v/>
-      </c>
-      <c r="I12" s="21">
-        <f>I10*I11</f>
-        <v/>
-      </c>
-      <c r="J12" s="21">
-        <f>J10*J11</f>
-        <v/>
-      </c>
-      <c r="K12" s="21">
-        <f>K10*K11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Sum of the explicit years</t>
-        </is>
-      </c>
-      <c r="B14" s="23">
-        <f>SUM(B12:K12)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>Present value</t>
+        </is>
+      </c>
+      <c r="B15" s="20">
+        <f>B13*B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="20">
+        <f>C13*C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="20">
+        <f>D13*D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="20">
+        <f>E13*E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="20">
+        <f>F13*F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Sum of the explicit years</t>
+        </is>
+      </c>
+      <c r="B17" s="23">
+        <f>SUM(B15:F15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>Terminal value, discounted</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
-        <v>25237.2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B18" s="23" t="n">
+        <v>38969.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B16" s="23">
-        <f>B14+B15</f>
+      <c r="B19" s="23">
+        <f>B17+B18</f>
         <v/>
       </c>
     </row>
